--- a/packages/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
+++ b/packages/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
@@ -504,7 +504,7 @@
         <v>913906</v>
       </c>
       <c r="G3" s="7">
-        <f>IF((E3&gt;0),((F3/E3)-1),0)</f>
+        <f>(IF((E3&lt;&gt;0),(F3/E3),0)-1)</f>
       </c>
       <c r="H3" s="8" t="s">
         <v>16</v>
@@ -542,7 +542,7 @@
         <v>253809</v>
       </c>
       <c r="G4" s="7">
-        <f>IF((E4&gt;0),((F4/E4)-1),0)</f>
+        <f>(IF((E4&lt;&gt;0),(F4/E4),0)-1)</f>
       </c>
       <c r="H4" s="8" t="s">
         <v>23</v>
@@ -580,7 +580,7 @@
         <v>554292</v>
       </c>
       <c r="G5" s="7">
-        <f>IF((E5&gt;0),((F5/E5)-1),0)</f>
+        <f>(IF((E5&lt;&gt;0),(F5/E5),0)-1)</f>
       </c>
       <c r="H5" s="8" t="s">
         <v>16</v>
@@ -618,7 +618,7 @@
         <v>1382992</v>
       </c>
       <c r="G6" s="7">
-        <f>IF((E6&gt;0),((F6/E6)-1),0)</f>
+        <f>(IF((E6&lt;&gt;0),(F6/E6),0)-1)</f>
       </c>
       <c r="H6" s="8" t="s">
         <v>33</v>
@@ -656,7 +656,7 @@
         <v>908011</v>
       </c>
       <c r="G7" s="7">
-        <f>IF((E7&gt;0),((F7/E7)-1),0)</f>
+        <f>(IF((E7&lt;&gt;0),(F7/E7),0)-1)</f>
       </c>
       <c r="H7" s="8" t="s">
         <v>23</v>
@@ -694,7 +694,7 @@
         <v>660566</v>
       </c>
       <c r="G8" s="7">
-        <f>IF((E8&gt;0),((F8/E8)-1),0)</f>
+        <f>(IF((E8&lt;&gt;0),(F8/E8),0)-1)</f>
       </c>
       <c r="H8" s="8" t="s">
         <v>33</v>
@@ -732,7 +732,7 @@
         <v>848349</v>
       </c>
       <c r="G9" s="7">
-        <f>IF((E9&gt;0),((F9/E9)-1),0)</f>
+        <f>(IF((E9&lt;&gt;0),(F9/E9),0)-1)</f>
       </c>
       <c r="H9" s="8" t="s">
         <v>33</v>
@@ -770,7 +770,7 @@
         <v>397547</v>
       </c>
       <c r="G10" s="7">
-        <f>IF((E10&gt;0),((F10/E10)-1),0)</f>
+        <f>(IF((E10&lt;&gt;0),(F10/E10),0)-1)</f>
       </c>
       <c r="H10" s="8" t="s">
         <v>16</v>
@@ -808,7 +808,7 @@
         <v>344031</v>
       </c>
       <c r="G11" s="7">
-        <f>IF((E11&gt;0),((F11/E11)-1),0)</f>
+        <f>(IF((E11&lt;&gt;0),(F11/E11),0)-1)</f>
       </c>
       <c r="H11" s="8" t="s">
         <v>23</v>
@@ -846,7 +846,7 @@
         <v>620563</v>
       </c>
       <c r="G12" s="7">
-        <f>IF((E12&gt;0),((F12/E12)-1),0)</f>
+        <f>(IF((E12&lt;&gt;0),(F12/E12),0)-1)</f>
       </c>
       <c r="H12" s="8" t="s">
         <v>33</v>
@@ -884,7 +884,7 @@
         <v>482532</v>
       </c>
       <c r="G13" s="7">
-        <f>IF((E13&gt;0),((F13/E13)-1),0)</f>
+        <f>(IF((E13&lt;&gt;0),(F13/E13),0)-1)</f>
       </c>
       <c r="H13" s="8" t="s">
         <v>16</v>
@@ -922,7 +922,7 @@
         <v>979180</v>
       </c>
       <c r="G14" s="7">
-        <f>IF((E14&gt;0),((F14/E14)-1),0)</f>
+        <f>(IF((E14&lt;&gt;0),(F14/E14),0)-1)</f>
       </c>
       <c r="H14" s="8" t="s">
         <v>23</v>
@@ -960,7 +960,7 @@
         <v>1229785</v>
       </c>
       <c r="G15" s="7">
-        <f>IF((E15&gt;0),((F15/E15)-1),0)</f>
+        <f>(IF((E15&lt;&gt;0),(F15/E15),0)-1)</f>
       </c>
       <c r="H15" s="8" t="s">
         <v>23</v>
@@ -998,7 +998,7 @@
         <v>272410</v>
       </c>
       <c r="G16" s="7">
-        <f>IF((E16&gt;0),((F16/E16)-1),0)</f>
+        <f>(IF((E16&lt;&gt;0),(F16/E16),0)-1)</f>
       </c>
       <c r="H16" s="8" t="s">
         <v>33</v>

--- a/packages/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
+++ b/packages/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Renewal Planner" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -445,6 +446,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
